--- a/LineClass/unfound_levels.xlsx
+++ b/LineClass/unfound_levels.xlsx
@@ -2,41 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UMD\AI\as-ai\LineClass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA2BE78-36F6-42F5-8BCA-2BE6FDFA177E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{12AA96E9-61CB-4EAD-BD28-1BAD31707AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1770" yWindow="1770" windowWidth="42315" windowHeight="17505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="46515" windowHeight="17505" xr2:uid="{03F36706-D499-451F-9EDD-451FE8FCE048}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="unfound_levels" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$O$660</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">unfound_levels!$A$1:$P$660</definedName>
   </definedNames>
-  <calcPr calcId="191029" refMode="R1C1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2657" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2664" uniqueCount="333">
   <si>
     <t>idx</t>
   </si>
@@ -1025,35 +1012,159 @@
     <t>f5d6d~3F2P</t>
   </si>
   <si>
-    <t>firm</t>
-  </si>
-  <si>
-    <t>weak</t>
-  </si>
-  <si>
-    <t>none</t>
+    <t>*</t>
+  </si>
+  <si>
+    <t>-</t>
   </si>
   <si>
     <t>?</t>
+  </si>
+  <si>
+    <t>7 lines, all free</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.000"/>
-  </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1062,12 +1173,185 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -1075,20 +1359,208 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="42">
+    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
+    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
+    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1111,44 +1583,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -1175,14 +1647,32 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -1209,6 +1699,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1220,190 +1728,173 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
+            <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{340280BB-C23B-4148-9856-4805700531A0}">
   <dimension ref="A1:R660"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -1499,7 +1990,7 @@
       <c r="O2">
         <v>8.3000000000000004E-2</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="P2" t="s">
         <v>329</v>
       </c>
     </row>
@@ -1549,8 +2040,8 @@
       <c r="O3">
         <v>9.2999999999999999E-2</v>
       </c>
-      <c r="Q3" t="s">
-        <v>330</v>
+      <c r="P3" t="s">
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -1599,14 +2090,8 @@
       <c r="O4">
         <v>6.9000000000000006E-2</v>
       </c>
-      <c r="P4" s="1">
-        <v>91197.845000000001</v>
-      </c>
-      <c r="Q4" s="2" t="s">
+      <c r="P4" t="s">
         <v>329</v>
-      </c>
-      <c r="R4" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -1655,8 +2140,8 @@
       <c r="O5">
         <v>6.6000000000000003E-2</v>
       </c>
-      <c r="Q5" t="s">
-        <v>331</v>
+      <c r="P5" t="s">
+        <v>330</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -1705,55 +2190,58 @@
       <c r="O6">
         <v>9.0999999999999998E-2</v>
       </c>
-      <c r="Q6" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7">
+      <c r="P6" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
         <v>719</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>4.5</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>117665.3</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="1">
         <v>32.200000000000003</v>
       </c>
-      <c r="H7" t="s">
-        <v>4</v>
-      </c>
-      <c r="I7">
+      <c r="H7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I7" s="1">
         <v>117</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="1">
         <v>28</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="1">
         <v>12</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="1">
         <v>15.9</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="1">
         <v>9680.9</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="1">
         <v>96370.41</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="1">
         <v>8.2000000000000003E-2</v>
+      </c>
+      <c r="P7" s="1">
+        <v>117712.656</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -1802,6 +2290,9 @@
       <c r="O8">
         <v>7.4999999999999997E-2</v>
       </c>
+      <c r="P8">
+        <v>90481.354999999996</v>
+      </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9">
@@ -1849,6 +2340,9 @@
       <c r="O9">
         <v>6.6000000000000003E-2</v>
       </c>
+      <c r="P9">
+        <v>116074.989</v>
+      </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10">
@@ -1896,6 +2390,9 @@
       <c r="O10">
         <v>9.8000000000000004E-2</v>
       </c>
+      <c r="P10" t="s">
+        <v>330</v>
+      </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11">
@@ -1943,6 +2440,9 @@
       <c r="O11">
         <v>7.8E-2</v>
       </c>
+      <c r="P11" t="s">
+        <v>330</v>
+      </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12">
@@ -1990,6 +2490,9 @@
       <c r="O12">
         <v>9.1999999999999998E-2</v>
       </c>
+      <c r="P12" t="s">
+        <v>330</v>
+      </c>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13">
@@ -2037,6 +2540,15 @@
       <c r="O13">
         <v>0.10199999999999999</v>
       </c>
+      <c r="P13">
+        <v>71767.231</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>331</v>
+      </c>
+      <c r="R13" t="s">
+        <v>332</v>
+      </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14">
@@ -2931,7 +3443,7 @@
         <v>7.0999999999999994E-2</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>672</v>
       </c>
@@ -2978,7 +3490,7 @@
         <v>9.7000000000000003E-2</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>521</v>
       </c>
@@ -3025,7 +3537,7 @@
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>488</v>
       </c>
@@ -3072,7 +3584,7 @@
         <v>9.9000000000000005E-2</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>661</v>
       </c>
@@ -3119,7 +3631,7 @@
         <v>8.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>632</v>
       </c>
@@ -3166,7 +3678,7 @@
         <v>6.5000000000000002E-2</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>944</v>
       </c>
@@ -3213,7 +3725,7 @@
         <v>0.12</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>315</v>
       </c>
@@ -3260,7 +3772,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>825</v>
       </c>
@@ -3307,7 +3819,7 @@
         <v>3.5999999999999997E-2</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>1010</v>
       </c>
@@ -3353,8 +3865,11 @@
       <c r="O41">
         <v>0.11700000000000001</v>
       </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P41" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>449</v>
       </c>
@@ -3401,7 +3916,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>710</v>
       </c>
@@ -3448,7 +3963,7 @@
         <v>9.0999999999999998E-2</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>1007</v>
       </c>
@@ -3494,8 +4009,11 @@
       <c r="O44">
         <v>9.5000000000000001E-2</v>
       </c>
-    </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P44">
+        <v>70477.790999999997</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>523</v>
       </c>
@@ -3542,7 +4060,7 @@
         <v>7.4999999999999997E-2</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>937</v>
       </c>
@@ -3589,7 +4107,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>432</v>
       </c>
@@ -3636,7 +4154,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>372</v>
       </c>
@@ -5939,7 +6457,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="97" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>339</v>
       </c>
@@ -5986,7 +6504,7 @@
         <v>0.106</v>
       </c>
     </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>376</v>
       </c>
@@ -6033,7 +6551,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="99" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>506</v>
       </c>
@@ -6080,7 +6598,7 @@
         <v>5.8999999999999997E-2</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>418</v>
       </c>
@@ -6127,7 +6645,7 @@
         <v>0.10100000000000001</v>
       </c>
     </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>484</v>
       </c>
@@ -6174,7 +6692,7 @@
         <v>7.1999999999999995E-2</v>
       </c>
     </row>
-    <row r="102" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>489</v>
       </c>
@@ -6221,7 +6739,7 @@
         <v>8.2000000000000003E-2</v>
       </c>
     </row>
-    <row r="103" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>212</v>
       </c>
@@ -6268,7 +6786,7 @@
         <v>0.192</v>
       </c>
     </row>
-    <row r="104" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>402</v>
       </c>
@@ -6315,7 +6833,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="105" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>209</v>
       </c>
@@ -6362,7 +6880,7 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="106" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>254</v>
       </c>
@@ -6409,7 +6927,7 @@
         <v>0.17499999999999999</v>
       </c>
     </row>
-    <row r="107" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>495</v>
       </c>
@@ -6456,7 +6974,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="108" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>832</v>
       </c>
@@ -6503,7 +7021,7 @@
         <v>0.11</v>
       </c>
     </row>
-    <row r="109" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>663</v>
       </c>
@@ -6550,7 +7068,7 @@
         <v>0.13100000000000001</v>
       </c>
     </row>
-    <row r="110" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>731</v>
       </c>
@@ -6597,54 +7115,57 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="111" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A111">
+    <row r="111" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="1">
         <v>718</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="C111">
+      <c r="C111" s="1">
         <v>3.5</v>
       </c>
-      <c r="D111" t="s">
-        <v>31</v>
-      </c>
-      <c r="E111" t="s">
+      <c r="D111" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E111" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="F111">
+      <c r="F111" s="1">
         <v>117700</v>
       </c>
-      <c r="G111">
+      <c r="G111" s="1">
         <v>404.2</v>
       </c>
-      <c r="H111" t="s">
-        <v>4</v>
-      </c>
-      <c r="I111">
+      <c r="H111" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I111" s="1">
         <v>128</v>
       </c>
-      <c r="J111">
+      <c r="J111" s="1">
         <v>17</v>
       </c>
-      <c r="K111">
-        <v>4</v>
-      </c>
-      <c r="L111">
+      <c r="K111" s="1">
+        <v>4</v>
+      </c>
+      <c r="L111" s="1">
         <v>10.15</v>
       </c>
-      <c r="M111">
+      <c r="M111" s="1">
         <v>12685.8</v>
       </c>
-      <c r="N111">
+      <c r="N111" s="1">
         <v>55637.35</v>
       </c>
-      <c r="O111">
+      <c r="O111" s="1">
         <v>6.5000000000000002E-2</v>
       </c>
-    </row>
-    <row r="112" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P111" s="1">
+        <v>117369.11500000001</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>716</v>
       </c>
@@ -8947,7 +9468,7 @@
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="161" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>736</v>
       </c>
@@ -8994,7 +9515,7 @@
         <v>8.5000000000000006E-2</v>
       </c>
     </row>
-    <row r="162" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>831</v>
       </c>
@@ -9041,7 +9562,7 @@
         <v>0.157</v>
       </c>
     </row>
-    <row r="163" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>657</v>
       </c>
@@ -9088,7 +9609,7 @@
         <v>7.2999999999999995E-2</v>
       </c>
     </row>
-    <row r="164" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>665</v>
       </c>
@@ -9135,7 +9656,7 @@
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
-    <row r="165" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>724</v>
       </c>
@@ -9181,8 +9702,14 @@
       <c r="O165">
         <v>6.4000000000000001E-2</v>
       </c>
-    </row>
-    <row r="166" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P165">
+        <v>117369.155</v>
+      </c>
+      <c r="Q165" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>623</v>
       </c>
@@ -9229,7 +9756,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="167" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>340</v>
       </c>
@@ -9276,7 +9803,7 @@
         <v>0.106</v>
       </c>
     </row>
-    <row r="168" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>706</v>
       </c>
@@ -9323,7 +9850,7 @@
         <v>9.1999999999999998E-2</v>
       </c>
     </row>
-    <row r="169" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>671</v>
       </c>
@@ -9370,7 +9897,7 @@
         <v>0.16300000000000001</v>
       </c>
     </row>
-    <row r="170" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>609</v>
       </c>
@@ -9417,7 +9944,7 @@
         <v>8.6999999999999994E-2</v>
       </c>
     </row>
-    <row r="171" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>864</v>
       </c>
@@ -9464,7 +9991,7 @@
         <v>8.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="172" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>573</v>
       </c>
@@ -9511,7 +10038,7 @@
         <v>0.107</v>
       </c>
     </row>
-    <row r="173" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>366</v>
       </c>
@@ -9558,7 +10085,7 @@
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>712</v>
       </c>
@@ -9605,7 +10132,7 @@
         <v>9.4E-2</v>
       </c>
     </row>
-    <row r="175" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>647</v>
       </c>
@@ -9652,7 +10179,7 @@
         <v>9.8000000000000004E-2</v>
       </c>
     </row>
-    <row r="176" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>478</v>
       </c>
@@ -17971,7 +18498,7 @@
         <v>0.26400000000000001</v>
       </c>
     </row>
-    <row r="353" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>581</v>
       </c>
@@ -18018,7 +18545,7 @@
         <v>0.105</v>
       </c>
     </row>
-    <row r="354" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>608</v>
       </c>
@@ -18065,7 +18592,7 @@
         <v>8.8999999999999996E-2</v>
       </c>
     </row>
-    <row r="355" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>606</v>
       </c>
@@ -18112,7 +18639,7 @@
         <v>0.10299999999999999</v>
       </c>
     </row>
-    <row r="356" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>206</v>
       </c>
@@ -18159,7 +18686,7 @@
         <v>2.5999999999999999E-2</v>
       </c>
     </row>
-    <row r="357" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>204</v>
       </c>
@@ -18206,7 +18733,7 @@
         <v>2.4E-2</v>
       </c>
     </row>
-    <row r="358" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>369</v>
       </c>
@@ -18253,7 +18780,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
-    <row r="359" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>654</v>
       </c>
@@ -18300,7 +18827,7 @@
         <v>8.4000000000000005E-2</v>
       </c>
     </row>
-    <row r="360" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>211</v>
       </c>
@@ -18347,7 +18874,7 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="361" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>194</v>
       </c>
@@ -18394,7 +18921,7 @@
         <v>0.25700000000000001</v>
       </c>
     </row>
-    <row r="362" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>403</v>
       </c>
@@ -18441,7 +18968,7 @@
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
-    <row r="363" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>1008</v>
       </c>
@@ -18487,8 +19014,11 @@
       <c r="O363">
         <v>9.9000000000000005E-2</v>
       </c>
-    </row>
-    <row r="364" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P363" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="364" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>792</v>
       </c>
@@ -18535,7 +19065,7 @@
         <v>6.2E-2</v>
       </c>
     </row>
-    <row r="365" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>78</v>
       </c>
@@ -18582,7 +19112,7 @@
         <v>4.1000000000000002E-2</v>
       </c>
     </row>
-    <row r="366" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>259</v>
       </c>
@@ -18629,7 +19159,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="367" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>433</v>
       </c>
@@ -18676,7 +19206,7 @@
         <v>8.1000000000000003E-2</v>
       </c>
     </row>
-    <row r="368" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>100</v>
       </c>
@@ -32448,7 +32978,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O660" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:P660" xr:uid="{340280BB-C23B-4148-9856-4805700531A0}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/LineClass/unfound_levels.xlsx
+++ b/LineClass/unfound_levels.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\UMD\AI\as-ai\LineClass\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{12AA96E9-61CB-4EAD-BD28-1BAD31707AB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC853B98-BA8B-44BE-8709-A236D46014A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="46515" windowHeight="17505" xr2:uid="{03F36706-D499-451F-9EDD-451FE8FCE048}"/>
+    <workbookView xWindow="2805" yWindow="2805" windowWidth="42315" windowHeight="17505" xr2:uid="{03F36706-D499-451F-9EDD-451FE8FCE048}"/>
   </bookViews>
   <sheets>
     <sheet name="unfound_levels" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2664" uniqueCount="333">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2670" uniqueCount="336">
   <si>
     <t>idx</t>
   </si>
@@ -1022,6 +1022,15 @@
   </si>
   <si>
     <t>7 lines, all free</t>
+  </si>
+  <si>
+    <t>6 lines, 1 dc</t>
+  </si>
+  <si>
+    <t>+</t>
+  </si>
+  <si>
+    <t>5 lines, 1 dc</t>
   </si>
 </sst>
 </file>
@@ -2596,6 +2605,15 @@
       <c r="O14">
         <v>0.10199999999999999</v>
       </c>
+      <c r="P14">
+        <v>131910.549</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>334</v>
+      </c>
+      <c r="R14" t="s">
+        <v>333</v>
+      </c>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15">
@@ -2643,6 +2661,15 @@
       <c r="O15">
         <v>7.4999999999999997E-2</v>
       </c>
+      <c r="P15">
+        <v>131776.4</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>334</v>
+      </c>
+      <c r="R15" t="s">
+        <v>335</v>
+      </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16">
@@ -2689,6 +2716,15 @@
       </c>
       <c r="O16">
         <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="P16">
+        <v>90050.031000000003</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>331</v>
+      </c>
+      <c r="R16" t="s">
+        <v>333</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
